--- a/assets/constructions/examples/ctd_the.xlsx
+++ b/assets/constructions/examples/ctd_the.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO6"/>
+  <dimension ref="A1:AS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,26 +634,46 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KM40TSSDUCR11</t>
+          <t>SRACR1616H08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SDUC 93</t>
+          <t>SRACR/L</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SSDUCR</t>
+          <t>SRACR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -666,52 +686,32 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>93</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>WID_DC11T3_H</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>WIDIA</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>DC..11T308</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>KENNA_KM40TS</t>
+          <t>ISO_5610:16X16</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ISO_DC11T3H</t>
+          <t>ISO_RC0803H</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>RACR1616H08</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>ZX</t>
+          <t>UX</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
@@ -731,13 +731,17 @@
       <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>16</v>
+      </c>
       <c r="AB2" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
@@ -758,29 +762,43 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>2021/https://www.machiningcloud.com/</t>
-        </is>
+          <t>2017/derek Металлорежущий инструмент и оснастка</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>26.11</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AS2" t="n">
+        <v>2140.34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>PALBIT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DSKNR 2525M 12-2</t>
+          <t>SVLCL 2020 K13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T-MaxⓇ shank tool for turning</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DSKN</t>
+          <t>SVLCL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -790,18 +808,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>S</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>-5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ISO_SN1207H</t>
+          <t>VCGT1303H</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -809,24 +827,18 @@
           <t>ISO</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>SNGQ 120708</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ISO_5610:25X25</t>
+          <t>ISO_5610:20X20</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ISO_SN1207H</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>10</v>
-      </c>
+          <t>ISO_VC1303H</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
         <v>0</v>
       </c>
@@ -835,29 +847,27 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>SKNR 2525M 12-2</t>
+          <t>VLCL2020K1303</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>ZAX</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
       <c r="U3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="W3" t="b">
-        <v>0</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
         <v>0</v>
       </c>
@@ -865,69 +875,79 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB3" t="n">
         <v>25</v>
       </c>
-      <c r="AA3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>32</v>
-      </c>
       <c r="AC3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
+        <v>125</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>28</v>
+      </c>
       <c r="AE3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-6</v>
-      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
       <c r="AL3" t="inlineStr">
         <is>
           <t>Steel</t>
         </is>
       </c>
-      <c r="AM3" t="n">
-        <v>0.725</v>
-      </c>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
-        </is>
+          <t>2020/Palbit General Catalogue</t>
+        </is>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>154.19</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AS3" t="n">
+        <v>14175.26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TAEGUTEC</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TCLNR 3232 P1207-F</t>
+          <t>PCBNR 3232P 19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TCLNR</t>
-        </is>
-      </c>
+          <t>T-MaxⓇ P shank tool for turning</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>N</t>
@@ -935,26 +955,30 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="H4" t="n">
-        <v>-5</v>
+        <v>15</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CN1207W</t>
+          <t>SAND_CN1906_H</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ISO</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>SANDVIK</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>CNMG 190612 (100deg)</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>ISO_5610:32X32</t>
@@ -962,10 +986,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ISO_CN1207W</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>ISO_CN1906H</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
@@ -974,27 +1000,25 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>CLNR3232P1207</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>ZX</t>
-        </is>
-      </c>
+          <t>CBNR 3232P 19</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="T4" t="b">
-        <v>0</v>
-      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="W4" t="b">
+        <v>0</v>
+      </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
@@ -1008,59 +1032,63 @@
         <v>32</v>
       </c>
       <c r="AB4" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AC4" t="n">
         <v>170</v>
       </c>
-      <c r="AD4" t="n">
-        <v>32</v>
-      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
         <v>32</v>
       </c>
       <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
+      <c r="AG4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-6</v>
+      </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
           <t>Steel</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr"/>
+      <c r="AM4" t="n">
+        <v>1.27</v>
+      </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2017/TaeguTec website</t>
-        </is>
-      </c>
+          <t>2021/www.sandvik.coromant.com</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>LIKON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CSDP R 2525 M12</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
+          <t>MDQNR3232P15</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CSDPR</t>
+          <t>MDQNR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1070,18 +1098,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>45</v>
+        <v>107.3</v>
       </c>
       <c r="H5" t="n">
-        <v>45</v>
+        <v>-17.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SP1203W</t>
+          <t>DN1504H</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1089,32 +1117,33 @@
           <t>ISO</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>DN_ _1504_ _
+DN_ _ 1506_ _</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ISO_5610:25X25</t>
+          <t>ISO_5610:32X32</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ISO_SP1203W</t>
+          <t>ISO_DN1504H</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>SDPR2525M1203</t>
+          <t>DQNR3232P15</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>ZX</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1122,14 +1151,14 @@
           <t>R</t>
         </is>
       </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
@@ -1137,33 +1166,29 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AB5" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="AC5" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AD5" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AE5" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
           <t>Steel</t>
@@ -1175,29 +1200,35 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2020/Palbit General Catalogue</t>
-        </is>
-      </c>
+          <t>2022/LIKON Инструментальный каталог</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>PALBIT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SRGCR2525M05</t>
+          <t>SRDC N 2525 M08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SRGCR/L</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SRGCR</t>
+          <t>SRDCN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1210,10 +1241,22 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RC0803M0H</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ISO</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
@@ -1222,30 +1265,36 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ISO_RC0502H</t>
+          <t>ISO_RC0803H</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>RGCR2525M05</t>
+          <t>RDCN2525M0803M0</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>ZX</t>
+          <t>U</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -1262,19 +1311,27 @@
         <v>25</v>
       </c>
       <c r="AB6" t="n">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="AC6" t="n">
         <v>150</v>
       </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>25</v>
+      </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
       <c r="AL6" t="inlineStr">
         <is>
           <t>Steel</t>
@@ -1286,8 +1343,22 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2017/derek Металлорежущий инструмент и оснастка</t>
-        </is>
+          <t>2020/Palbit General Catalogue</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>147.42</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AS6" t="n">
+        <v>13552.87</v>
       </c>
     </row>
   </sheetData>
